--- a/output/yearly_benthic_cover_iteration_48_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_48_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.19103110087732</v>
+        <v>45.78329017819993</v>
       </c>
       <c r="M2" t="n">
-        <v>99.78819234742375</v>
+        <v>98.83795409588029</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.08209493047865</v>
+        <v>88.00542043477695</v>
       </c>
       <c r="C3" t="n">
-        <v>45.94884858030243</v>
+        <v>45.92276667993909</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228855789751637</v>
+        <v>2.228678942186709</v>
       </c>
       <c r="E3" t="n">
-        <v>5.720878088555772</v>
+        <v>5.701751584934256</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429519299172125</v>
+        <v>0.742892980728903</v>
       </c>
       <c r="G3" t="n">
-        <v>33.9795463545372</v>
+        <v>33.9713027698725</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17578877619177</v>
+        <v>34.17307711352953</v>
       </c>
       <c r="I3" t="n">
-        <v>6.590624429542467</v>
+        <v>6.544635913969413</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643449561982578</v>
+        <v>4.643081129555643</v>
       </c>
       <c r="K3" t="n">
-        <v>11.91790506952136</v>
+        <v>11.99457956522304</v>
       </c>
       <c r="L3" t="n">
-        <v>48.89669001629956</v>
+        <v>48.84772944016569</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7634436661234</v>
+        <v>106.7650756853278</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.20867943025164</v>
+        <v>87.06730310946463</v>
       </c>
       <c r="C4" t="n">
-        <v>42.71418116663796</v>
+        <v>42.61548616268356</v>
       </c>
       <c r="D4" t="n">
-        <v>2.187018303913831</v>
+        <v>2.183340932655548</v>
       </c>
       <c r="E4" t="n">
-        <v>6.530782552119324</v>
+        <v>6.496639982771832</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445148534107042</v>
+        <v>0.7444473775605119</v>
       </c>
       <c r="G4" t="n">
-        <v>33.34172187261257</v>
+        <v>33.280224651974</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24768325689239</v>
+        <v>34.24457936778354</v>
       </c>
       <c r="I4" t="n">
-        <v>5.503740757485914</v>
+        <v>5.465274686966002</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653217833816901</v>
+        <v>4.652796109753199</v>
       </c>
       <c r="K4" t="n">
-        <v>12.79132056974835</v>
+        <v>12.93269689053537</v>
       </c>
       <c r="L4" t="n">
-        <v>44.31142536279307</v>
+        <v>44.27002150472634</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81692709917938</v>
+        <v>99.81820455794528</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.10348615368156</v>
+        <v>85.82430707749901</v>
       </c>
       <c r="C5" t="n">
-        <v>42.46325274402606</v>
+        <v>42.22072284174156</v>
       </c>
       <c r="D5" t="n">
-        <v>2.133338138105067</v>
+        <v>2.122417672293809</v>
       </c>
       <c r="E5" t="n">
-        <v>7.136253190826729</v>
+        <v>7.075770786109543</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458391336530628</v>
+        <v>0.7457665515786371</v>
       </c>
       <c r="G5" t="n">
-        <v>32.52335233484119</v>
+        <v>32.35158370495373</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30860014804089</v>
+        <v>34.3052613726173</v>
       </c>
       <c r="I5" t="n">
-        <v>4.594608622882991</v>
+        <v>4.562466042579518</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661494585331643</v>
+        <v>4.661040947366481</v>
       </c>
       <c r="K5" t="n">
-        <v>13.89651384631843</v>
+        <v>14.17569292250098</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48735172194755</v>
+        <v>43.45177105000841</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84711831229205</v>
+        <v>99.84818681425097</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.73260566899657</v>
+        <v>84.34531133673318</v>
       </c>
       <c r="C6" t="n">
-        <v>41.80604239925258</v>
+        <v>41.45021881341702</v>
       </c>
       <c r="D6" t="n">
-        <v>2.066473589732676</v>
+        <v>2.049948803153699</v>
       </c>
       <c r="E6" t="n">
-        <v>7.5516865760347</v>
+        <v>7.468801618384168</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469642444030057</v>
+        <v>0.7468888081328359</v>
       </c>
       <c r="G6" t="n">
-        <v>31.50398310003392</v>
+        <v>31.24695537632895</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36035524253826</v>
+        <v>34.35688517411045</v>
       </c>
       <c r="I6" t="n">
-        <v>3.834616388735212</v>
+        <v>3.807776505792861</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668526527518786</v>
+        <v>4.668055050830223</v>
       </c>
       <c r="K6" t="n">
-        <v>15.26739433100343</v>
+        <v>15.65468866326682</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79893525244169</v>
+        <v>42.76835735546671</v>
       </c>
       <c r="M6" t="n">
-        <v>99.8723719826977</v>
+        <v>99.87326483215057</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.1651888354335</v>
+        <v>82.59992525829257</v>
       </c>
       <c r="C7" t="n">
-        <v>40.83427628618781</v>
+        <v>40.29606637558583</v>
       </c>
       <c r="D7" t="n">
-        <v>1.990256720447314</v>
+        <v>1.964695974685295</v>
       </c>
       <c r="E7" t="n">
-        <v>7.806429536271656</v>
+        <v>7.687726642320651</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479221754635623</v>
+        <v>0.7478464469232768</v>
       </c>
       <c r="G7" t="n">
-        <v>30.34203504812867</v>
+        <v>29.94746373889886</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40442007132387</v>
+        <v>34.40093655847073</v>
       </c>
       <c r="I7" t="n">
-        <v>3.199611687151157</v>
+        <v>3.177215603723287</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674513596647265</v>
+        <v>4.67404029327048</v>
       </c>
       <c r="K7" t="n">
-        <v>16.83481116456649</v>
+        <v>17.40007474170743</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22439542733639</v>
+        <v>42.19808731310139</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89348287809069</v>
+        <v>99.89422843039465</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.90810259931185</v>
+        <v>87.53602910522496</v>
       </c>
       <c r="C8" t="n">
-        <v>43.10659338366618</v>
+        <v>42.63681888629907</v>
       </c>
       <c r="D8" t="n">
-        <v>1.994444877628921</v>
+        <v>1.968921869815148</v>
       </c>
       <c r="E8" t="n">
-        <v>9.61425056318939</v>
+        <v>9.547406446837913</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494960506316596</v>
+        <v>0.7494550014775954</v>
       </c>
       <c r="G8" t="n">
-        <v>30.83911239543904</v>
+        <v>30.46274376506281</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47681832905634</v>
+        <v>34.47493006796938</v>
       </c>
       <c r="I8" t="n">
-        <v>5.549630066918607</v>
+        <v>5.648478194827145</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684350316447873</v>
+        <v>4.68409375923497</v>
       </c>
       <c r="K8" t="n">
-        <v>12.09189740068816</v>
+        <v>12.46397089477504</v>
       </c>
       <c r="L8" t="n">
-        <v>44.61691000443034</v>
+        <v>44.71133172321026</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81540078878467</v>
+        <v>99.81212150428436</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.77046668551792</v>
+        <v>85.26566109454463</v>
       </c>
       <c r="C9" t="n">
-        <v>41.83044992683381</v>
+        <v>41.24266993290578</v>
       </c>
       <c r="D9" t="n">
-        <v>1.897416562267587</v>
+        <v>1.865869510644708</v>
       </c>
       <c r="E9" t="n">
-        <v>9.918693941347748</v>
+        <v>9.833657242854498</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508455552487968</v>
+        <v>0.7508366585372886</v>
       </c>
       <c r="G9" t="n">
-        <v>29.33881165685678</v>
+        <v>28.86833940604725</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53889554144466</v>
+        <v>34.53848629271527</v>
       </c>
       <c r="I9" t="n">
-        <v>4.633018708047373</v>
+        <v>4.715742867887551</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692784720304982</v>
+        <v>4.692729115858053</v>
       </c>
       <c r="K9" t="n">
-        <v>14.22953331448206</v>
+        <v>14.73433890545539</v>
       </c>
       <c r="L9" t="n">
-        <v>43.78586036793639</v>
+        <v>43.8660889895603</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84584360925226</v>
+        <v>99.84309782792147</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.46685282850598</v>
+        <v>82.85476009495864</v>
       </c>
       <c r="C10" t="n">
-        <v>40.24562867927109</v>
+        <v>39.56276610570438</v>
       </c>
       <c r="D10" t="n">
-        <v>1.793976264157108</v>
+        <v>1.75776207134139</v>
       </c>
       <c r="E10" t="n">
-        <v>10.02243107748974</v>
+        <v>9.919902045402416</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520050486220961</v>
+        <v>0.7520256063168439</v>
       </c>
       <c r="G10" t="n">
-        <v>27.73936560776907</v>
+        <v>27.19572391374067</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59223223661643</v>
+        <v>34.59317789057481</v>
       </c>
       <c r="I10" t="n">
-        <v>3.866811039963455</v>
+        <v>3.936008528102238</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700031553888102</v>
+        <v>4.700160039480273</v>
       </c>
       <c r="K10" t="n">
-        <v>16.53314717149401</v>
+        <v>17.14523990504136</v>
       </c>
       <c r="L10" t="n">
-        <v>43.09252918512246</v>
+        <v>43.16100113181295</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87130503588756</v>
+        <v>99.86900714255867</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.09293544904</v>
+        <v>80.35173071293679</v>
       </c>
       <c r="C11" t="n">
-        <v>38.47091770745585</v>
+        <v>37.66905210590478</v>
       </c>
       <c r="D11" t="n">
-        <v>1.688548353518873</v>
+        <v>1.646821850360523</v>
       </c>
       <c r="E11" t="n">
-        <v>9.971204955410139</v>
+        <v>9.841225396973275</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530024358640012</v>
+        <v>0.7530502721713928</v>
       </c>
       <c r="G11" t="n">
-        <v>26.10918609152487</v>
+        <v>25.4792802209816</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63811204974406</v>
+        <v>34.64031251988406</v>
       </c>
       <c r="I11" t="n">
-        <v>3.226616338828059</v>
+        <v>3.284476251494724</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706265224150009</v>
+        <v>4.706564201071203</v>
       </c>
       <c r="K11" t="n">
-        <v>18.90706455095999</v>
+        <v>19.64826928706321</v>
       </c>
       <c r="L11" t="n">
-        <v>42.51460632380741</v>
+        <v>42.57334503680695</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89258858222324</v>
+        <v>99.89066642977494</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.67292994753097</v>
+        <v>77.78233867619397</v>
       </c>
       <c r="C12" t="n">
-        <v>36.55007749297943</v>
+        <v>35.60716296089603</v>
       </c>
       <c r="D12" t="n">
-        <v>1.58215885074895</v>
+        <v>1.534159986253698</v>
       </c>
       <c r="E12" t="n">
-        <v>9.791606628811646</v>
+        <v>9.624683509164203</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538612732412682</v>
+        <v>0.7539346061385988</v>
       </c>
       <c r="G12" t="n">
-        <v>24.4641379528583</v>
+        <v>23.73619962901136</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67761856909834</v>
+        <v>34.68099188237553</v>
       </c>
       <c r="I12" t="n">
-        <v>2.691913715014547</v>
+        <v>2.740277774884352</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711632957757928</v>
+        <v>4.712091288366239</v>
       </c>
       <c r="K12" t="n">
-        <v>21.32707005246901</v>
+        <v>22.21766132380602</v>
       </c>
       <c r="L12" t="n">
-        <v>42.03322422291745</v>
+        <v>42.08394026386753</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91037176836589</v>
+        <v>99.90876454856958</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.22954974998014</v>
+        <v>75.27289297059539</v>
       </c>
       <c r="C13" t="n">
-        <v>34.52226141297244</v>
+        <v>33.52012616036988</v>
       </c>
       <c r="D13" t="n">
-        <v>1.475736967513267</v>
+        <v>1.425273538947357</v>
       </c>
       <c r="E13" t="n">
-        <v>9.507230793350843</v>
+        <v>9.322554492323956</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546014798057836</v>
+        <v>0.7546977853915392</v>
       </c>
       <c r="G13" t="n">
-        <v>22.81858913110232</v>
+        <v>22.05153148923776</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71166807106605</v>
+        <v>34.71609812801079</v>
       </c>
       <c r="I13" t="n">
-        <v>2.245464058355723</v>
+        <v>2.285876377986877</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716259248786149</v>
+        <v>4.716861158697117</v>
       </c>
       <c r="K13" t="n">
-        <v>23.77045025001986</v>
+        <v>24.72710702940461</v>
       </c>
       <c r="L13" t="n">
-        <v>41.63251295603506</v>
+        <v>41.67664798314539</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92522461902736</v>
+        <v>99.92388117291988</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.32945274299112</v>
+        <v>82.66612508913971</v>
       </c>
       <c r="C14" t="n">
-        <v>38.92328631014527</v>
+        <v>38.03948691720342</v>
       </c>
       <c r="D14" t="n">
-        <v>1.477475601882784</v>
+        <v>1.4270609894178</v>
       </c>
       <c r="E14" t="n">
-        <v>11.95000399313341</v>
+        <v>11.83895455616532</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554905109115707</v>
+        <v>0.7556442597872796</v>
       </c>
       <c r="G14" t="n">
-        <v>24.78617353844654</v>
+        <v>24.06553283071963</v>
       </c>
       <c r="H14" t="n">
-        <v>36.69326426794975</v>
+        <v>36.74598223513578</v>
       </c>
       <c r="I14" t="n">
-        <v>2.945229137469757</v>
+        <v>3.110173594243403</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721815693197319</v>
+        <v>4.722776623670494</v>
       </c>
       <c r="K14" t="n">
-        <v>16.67054725700888</v>
+        <v>17.33387491086028</v>
       </c>
       <c r="L14" t="n">
-        <v>44.30810765587016</v>
+        <v>44.52309557265291</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90194122302431</v>
+        <v>99.8964574007166</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.55315538081204</v>
+        <v>81.79915350899643</v>
       </c>
       <c r="C15" t="n">
-        <v>38.59611684565887</v>
+        <v>37.63539845246778</v>
       </c>
       <c r="D15" t="n">
-        <v>1.448224934757041</v>
+        <v>1.393465672511673</v>
       </c>
       <c r="E15" t="n">
-        <v>12.1286811805851</v>
+        <v>12.00948065504063</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562399606842157</v>
+        <v>0.7564431914587023</v>
       </c>
       <c r="G15" t="n">
-        <v>24.301258280299</v>
+        <v>23.51580029215611</v>
       </c>
       <c r="H15" t="n">
-        <v>36.73545892254881</v>
+        <v>36.80164213830314</v>
       </c>
       <c r="I15" t="n">
-        <v>2.456792347661529</v>
+        <v>2.594551612909272</v>
       </c>
       <c r="J15" t="n">
-        <v>4.72649975427635</v>
+        <v>4.727769946616887</v>
       </c>
       <c r="K15" t="n">
-        <v>17.44684461918796</v>
+        <v>18.2008464910036</v>
       </c>
       <c r="L15" t="n">
-        <v>43.87522661466792</v>
+        <v>44.0773613455774</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91818807951474</v>
+        <v>99.91360628904877</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.01710471120167</v>
+        <v>79.19590220903034</v>
       </c>
       <c r="C16" t="n">
-        <v>36.43957484611244</v>
+        <v>35.4322929018829</v>
       </c>
       <c r="D16" t="n">
-        <v>1.352415598255304</v>
+        <v>1.296387993881898</v>
       </c>
       <c r="E16" t="n">
-        <v>11.66780381913038</v>
+        <v>11.53350649811175</v>
       </c>
       <c r="F16" t="n">
-        <v>0.756885486022839</v>
+        <v>0.7571322066915556</v>
       </c>
       <c r="G16" t="n">
-        <v>22.69357471118314</v>
+        <v>21.87754012650083</v>
       </c>
       <c r="H16" t="n">
-        <v>36.7668162572485</v>
+        <v>36.83516334956344</v>
       </c>
       <c r="I16" t="n">
-        <v>2.049074551718762</v>
+        <v>2.164095742458648</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730534287642746</v>
+        <v>4.732076291822219</v>
       </c>
       <c r="K16" t="n">
-        <v>19.98289528879832</v>
+        <v>20.80409779096965</v>
       </c>
       <c r="L16" t="n">
-        <v>43.50928563320977</v>
+        <v>43.69153842901109</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93175576812052</v>
+        <v>99.92792912186364</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.80740018971207</v>
+        <v>81.11173376648279</v>
       </c>
       <c r="C17" t="n">
-        <v>37.72962844636421</v>
+        <v>36.79171461875883</v>
       </c>
       <c r="D17" t="n">
-        <v>1.353548211670274</v>
+        <v>1.2975606760303</v>
       </c>
       <c r="E17" t="n">
-        <v>12.47885589491651</v>
+        <v>12.39154301347087</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575193582261552</v>
+        <v>0.7578170907131276</v>
       </c>
       <c r="G17" t="n">
-        <v>23.17130257875091</v>
+        <v>22.37807475995553</v>
       </c>
       <c r="H17" t="n">
-        <v>37.25633010405797</v>
+        <v>37.34922829787681</v>
       </c>
       <c r="I17" t="n">
-        <v>2.055348053176782</v>
+        <v>2.201153111479111</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734495988913472</v>
+        <v>4.736356816957045</v>
       </c>
       <c r="K17" t="n">
-        <v>18.19259981028792</v>
+        <v>18.88826623351721</v>
       </c>
       <c r="L17" t="n">
-        <v>44.00931747027522</v>
+        <v>44.24671368773967</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93154572692735</v>
+        <v>99.92669454001572</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.39687578156672</v>
+        <v>78.58338981635077</v>
       </c>
       <c r="C18" t="n">
-        <v>35.63616664280414</v>
+        <v>34.60236729996545</v>
       </c>
       <c r="D18" t="n">
-        <v>1.266284880065383</v>
+        <v>1.207539969792935</v>
       </c>
       <c r="E18" t="n">
-        <v>11.96001376092916</v>
+        <v>11.83781023174084</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580644700518083</v>
+        <v>0.7584071823105919</v>
       </c>
       <c r="G18" t="n">
-        <v>21.67744735939994</v>
+        <v>20.82555384025041</v>
       </c>
       <c r="H18" t="n">
-        <v>37.28313980324205</v>
+        <v>37.3783111281012</v>
       </c>
       <c r="I18" t="n">
-        <v>1.714022570054585</v>
+        <v>1.835722574713619</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737902937823804</v>
+        <v>4.740044889441196</v>
       </c>
       <c r="K18" t="n">
-        <v>20.60312421843329</v>
+        <v>21.41661018364923</v>
       </c>
       <c r="L18" t="n">
-        <v>43.70361613728543</v>
+        <v>43.91987937439977</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94290699852286</v>
+        <v>99.93885685801445</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.47199090434987</v>
+        <v>77.64971829718094</v>
       </c>
       <c r="C19" t="n">
-        <v>34.97498428351481</v>
+        <v>33.93734539796625</v>
       </c>
       <c r="D19" t="n">
-        <v>1.233479062299053</v>
+        <v>1.174482353519978</v>
       </c>
       <c r="E19" t="n">
-        <v>11.88836724460075</v>
+        <v>11.7710081806375</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585246938669301</v>
+        <v>0.7589097348385533</v>
       </c>
       <c r="G19" t="n">
-        <v>21.1158467283674</v>
+        <v>20.25543344279405</v>
       </c>
       <c r="H19" t="n">
-        <v>37.30577453883227</v>
+        <v>37.40307957068256</v>
       </c>
       <c r="I19" t="n">
-        <v>1.429219299715155</v>
+        <v>1.543619171967329</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740779336668314</v>
+        <v>4.743185842740955</v>
       </c>
       <c r="K19" t="n">
-        <v>21.52800909565012</v>
+        <v>22.35028170281908</v>
       </c>
       <c r="L19" t="n">
-        <v>43.44939488277801</v>
+        <v>43.6609529998059</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95238826194294</v>
+        <v>99.94858010059123</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.85728260867526</v>
+        <v>75.14250155764431</v>
       </c>
       <c r="C20" t="n">
-        <v>32.58001211397551</v>
+        <v>31.66700852391558</v>
       </c>
       <c r="D20" t="n">
-        <v>1.139875705913863</v>
+        <v>1.086409520615946</v>
       </c>
       <c r="E20" t="n">
-        <v>11.18481743047303</v>
+        <v>11.10283025971381</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589218819092129</v>
+        <v>0.7593430361750665</v>
       </c>
       <c r="G20" t="n">
-        <v>19.51345704288183</v>
+        <v>18.73650606201276</v>
       </c>
       <c r="H20" t="n">
-        <v>37.32530904795865</v>
+        <v>37.42443494883058</v>
       </c>
       <c r="I20" t="n">
-        <v>1.191639737606089</v>
+        <v>1.287083754201972</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743261761932582</v>
+        <v>4.745893976094163</v>
       </c>
       <c r="K20" t="n">
-        <v>24.14271739132473</v>
+        <v>24.85749844235571</v>
       </c>
       <c r="L20" t="n">
-        <v>43.23756995859655</v>
+        <v>43.4326147233963</v>
       </c>
       <c r="M20" t="n">
-        <v>99.9602994638968</v>
+        <v>99.95712168966759</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.87846890602253</v>
+        <v>81.62035761709897</v>
       </c>
       <c r="C21" t="n">
-        <v>36.326926339667</v>
+        <v>35.70042236447174</v>
       </c>
       <c r="D21" t="n">
-        <v>1.140666629736137</v>
+        <v>1.087223678508566</v>
       </c>
       <c r="E21" t="n">
-        <v>13.20083159783281</v>
+        <v>13.2732382684263</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594484738810677</v>
+        <v>0.7599120896621507</v>
       </c>
       <c r="G21" t="n">
-        <v>21.25118574734183</v>
+        <v>20.60680230976309</v>
       </c>
       <c r="H21" t="n">
-        <v>39.07539683507699</v>
+        <v>39.30873597517609</v>
       </c>
       <c r="I21" t="n">
-        <v>1.704386660397014</v>
+        <v>1.834994735174328</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746552961756675</v>
+        <v>4.749450560388439</v>
       </c>
       <c r="K21" t="n">
-        <v>18.1215310939775</v>
+        <v>18.37964238290103</v>
       </c>
       <c r="L21" t="n">
-        <v>45.49476907101443</v>
+        <v>45.85881456544389</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94322650465892</v>
+        <v>99.93887931281667</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_48_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_48_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.78329017819993</v>
+        <v>45.81165997138676</v>
       </c>
       <c r="M2" t="n">
-        <v>98.83795409588029</v>
+        <v>98.3682988271843</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.00542043477695</v>
+        <v>88.09942277745859</v>
       </c>
       <c r="C3" t="n">
-        <v>45.92276667993909</v>
+        <v>45.95376604546992</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228678942186709</v>
+        <v>2.228896457568935</v>
       </c>
       <c r="E3" t="n">
-        <v>5.701751584934256</v>
+        <v>5.724646717346261</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742892980728903</v>
+        <v>0.7429654858563117</v>
       </c>
       <c r="G3" t="n">
-        <v>33.9713027698725</v>
+        <v>33.98106898535329</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17307711352953</v>
+        <v>34.17641234939033</v>
       </c>
       <c r="I3" t="n">
-        <v>6.544635913969413</v>
+        <v>6.601898495341517</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643081129555643</v>
+        <v>4.643534286601948</v>
       </c>
       <c r="K3" t="n">
-        <v>11.99457956522304</v>
+        <v>11.9005772225414</v>
       </c>
       <c r="L3" t="n">
-        <v>48.84772944016569</v>
+        <v>48.90870006321484</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7650756853278</v>
+        <v>106.7630433312262</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.06730310946463</v>
+        <v>87.20381064139082</v>
       </c>
       <c r="C4" t="n">
-        <v>42.61548616268356</v>
+        <v>42.69889585663223</v>
       </c>
       <c r="D4" t="n">
-        <v>2.183340932655548</v>
+        <v>2.185889976398677</v>
       </c>
       <c r="E4" t="n">
-        <v>6.496639982771832</v>
+        <v>6.533052531514602</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444473775605119</v>
+        <v>0.7445312047178082</v>
       </c>
       <c r="G4" t="n">
-        <v>33.280224651974</v>
+        <v>33.32540541762624</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24457936778354</v>
+        <v>34.24843541701917</v>
       </c>
       <c r="I4" t="n">
-        <v>5.465274686966002</v>
+        <v>5.513176064628031</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652796109753199</v>
+        <v>4.653320029486301</v>
       </c>
       <c r="K4" t="n">
-        <v>12.93269689053537</v>
+        <v>12.79618935860917</v>
       </c>
       <c r="L4" t="n">
-        <v>44.27002150472634</v>
+        <v>44.32152871544355</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81820455794528</v>
+        <v>99.81661393068495</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.82430707749901</v>
+        <v>86.18462051171036</v>
       </c>
       <c r="C5" t="n">
-        <v>42.22072284174156</v>
+        <v>42.53540789844186</v>
       </c>
       <c r="D5" t="n">
-        <v>2.122417672293809</v>
+        <v>2.136698934686172</v>
       </c>
       <c r="E5" t="n">
-        <v>7.075770786109543</v>
+        <v>7.15311534023625</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457665515786371</v>
+        <v>0.7458565373406054</v>
       </c>
       <c r="G5" t="n">
-        <v>32.35158370495373</v>
+        <v>32.57545394445768</v>
       </c>
       <c r="H5" t="n">
-        <v>34.3052613726173</v>
+        <v>34.30940071766785</v>
       </c>
       <c r="I5" t="n">
-        <v>4.562466042579518</v>
+        <v>4.602491678943029</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661040947366481</v>
+        <v>4.661603358378784</v>
       </c>
       <c r="K5" t="n">
-        <v>14.17569292250098</v>
+        <v>13.81537948828964</v>
       </c>
       <c r="L5" t="n">
-        <v>43.45177105000841</v>
+        <v>43.4960688336955</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84818681425097</v>
+        <v>99.846856220427</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.34531133673318</v>
+        <v>84.96957858720195</v>
       </c>
       <c r="C6" t="n">
-        <v>41.45021881341702</v>
+        <v>42.03531778762105</v>
       </c>
       <c r="D6" t="n">
-        <v>2.049948803153699</v>
+        <v>2.077812543394753</v>
       </c>
       <c r="E6" t="n">
-        <v>7.468801618384168</v>
+        <v>7.596177145068624</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468888081328359</v>
+        <v>0.7469804596402064</v>
       </c>
       <c r="G6" t="n">
-        <v>31.24695537632895</v>
+        <v>31.67769015737053</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35688517411045</v>
+        <v>34.3611011434495</v>
       </c>
       <c r="I6" t="n">
-        <v>3.807776505792861</v>
+        <v>3.841189265527049</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668055050830223</v>
+        <v>4.668627872751291</v>
       </c>
       <c r="K6" t="n">
-        <v>15.65468866326682</v>
+        <v>15.03042141279805</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76835735546671</v>
+        <v>42.80641380849916</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87326483215057</v>
+        <v>99.87215300891826</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.59992525829257</v>
+        <v>83.594437759543</v>
       </c>
       <c r="C7" t="n">
-        <v>40.29606637558583</v>
+        <v>41.25701798691614</v>
       </c>
       <c r="D7" t="n">
-        <v>1.964695974685295</v>
+        <v>2.011282549148271</v>
       </c>
       <c r="E7" t="n">
-        <v>7.687726642320651</v>
+        <v>7.887133603775275</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478464469232768</v>
+        <v>0.7479351218955668</v>
       </c>
       <c r="G7" t="n">
-        <v>29.94746373889886</v>
+        <v>30.66339435354003</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40093655847073</v>
+        <v>34.40501560719608</v>
       </c>
       <c r="I7" t="n">
-        <v>3.177215603723287</v>
+        <v>3.205082012140493</v>
       </c>
       <c r="J7" t="n">
-        <v>4.67404029327048</v>
+        <v>4.674594511847293</v>
       </c>
       <c r="K7" t="n">
-        <v>17.40007474170743</v>
+        <v>16.405562240457</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19808731310139</v>
+        <v>42.23072007080665</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89422843039465</v>
+        <v>99.8933002981798</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.53602910522496</v>
+        <v>88.58277230325776</v>
       </c>
       <c r="C8" t="n">
-        <v>42.63681888629907</v>
+        <v>43.64821738735294</v>
       </c>
       <c r="D8" t="n">
-        <v>1.968921869815148</v>
+        <v>2.015580009566738</v>
       </c>
       <c r="E8" t="n">
-        <v>9.547406446837913</v>
+        <v>9.781752634744407</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494550014775954</v>
+        <v>0.7495332173910447</v>
       </c>
       <c r="G8" t="n">
-        <v>30.46274376506281</v>
+        <v>31.1946136516699</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47493006796938</v>
+        <v>34.47852799998806</v>
       </c>
       <c r="I8" t="n">
-        <v>5.648478194827145</v>
+        <v>5.678182181203586</v>
       </c>
       <c r="J8" t="n">
-        <v>4.68409375923497</v>
+        <v>4.68458260869403</v>
       </c>
       <c r="K8" t="n">
-        <v>12.46397089477504</v>
+        <v>11.41722769674223</v>
       </c>
       <c r="L8" t="n">
-        <v>44.71133172321026</v>
+        <v>44.74568572890931</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81212150428436</v>
+        <v>99.81113081300448</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.26566109454463</v>
+        <v>86.83567460605349</v>
       </c>
       <c r="C9" t="n">
-        <v>41.24266993290578</v>
+        <v>42.78301823022389</v>
       </c>
       <c r="D9" t="n">
-        <v>1.865869510644708</v>
+        <v>1.937189980606987</v>
       </c>
       <c r="E9" t="n">
-        <v>9.833657242854498</v>
+        <v>10.19139175901993</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508366585372886</v>
+        <v>0.750897137989152</v>
       </c>
       <c r="G9" t="n">
-        <v>28.86833940604725</v>
+        <v>29.98139132562178</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53848629271527</v>
+        <v>34.541268347501</v>
       </c>
       <c r="I9" t="n">
-        <v>4.715742867887551</v>
+        <v>4.740428942882449</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692729115858053</v>
+        <v>4.693107112432201</v>
       </c>
       <c r="K9" t="n">
-        <v>14.73433890545539</v>
+        <v>13.16432539394648</v>
       </c>
       <c r="L9" t="n">
-        <v>43.8660889895603</v>
+        <v>43.89492909301841</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84309782792147</v>
+        <v>99.84227271718879</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.85476009495864</v>
+        <v>84.85047083206955</v>
       </c>
       <c r="C10" t="n">
-        <v>39.56276610570438</v>
+        <v>41.53405933798754</v>
       </c>
       <c r="D10" t="n">
-        <v>1.75776207134139</v>
+        <v>1.848733451496162</v>
       </c>
       <c r="E10" t="n">
-        <v>9.919902045402416</v>
+        <v>10.3854457313671</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520256063168439</v>
+        <v>0.7520642588550392</v>
       </c>
       <c r="G10" t="n">
-        <v>27.19572391374067</v>
+        <v>28.61237236458683</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59317789057481</v>
+        <v>34.59495590733181</v>
       </c>
       <c r="I10" t="n">
-        <v>3.936008528102238</v>
+        <v>3.956497500588612</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700160039480273</v>
+        <v>4.700401617843996</v>
       </c>
       <c r="K10" t="n">
-        <v>17.14523990504136</v>
+        <v>15.14952916793046</v>
       </c>
       <c r="L10" t="n">
-        <v>43.16100113181295</v>
+        <v>43.18473291233524</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86900714255867</v>
+        <v>99.86832141825325</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.35173071293679</v>
+        <v>82.78661179754089</v>
       </c>
       <c r="C11" t="n">
-        <v>37.66905210590478</v>
+        <v>40.0842703135249</v>
       </c>
       <c r="D11" t="n">
-        <v>1.646821850360523</v>
+        <v>1.757655617144975</v>
       </c>
       <c r="E11" t="n">
-        <v>9.841225396973275</v>
+        <v>10.42405086872862</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530502721713928</v>
+        <v>0.7530639829588615</v>
       </c>
       <c r="G11" t="n">
-        <v>25.4792802209816</v>
+        <v>27.20278413622035</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64031251988406</v>
+        <v>34.64094321610763</v>
       </c>
       <c r="I11" t="n">
-        <v>3.284476251494724</v>
+        <v>3.301464082887562</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706564201071203</v>
+        <v>4.706649893492885</v>
       </c>
       <c r="K11" t="n">
-        <v>19.64826928706321</v>
+        <v>17.21338820245911</v>
       </c>
       <c r="L11" t="n">
-        <v>42.57334503680695</v>
+        <v>42.59243877566631</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89066642977494</v>
+        <v>99.89009729165032</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.78233867619397</v>
+        <v>80.62529063551719</v>
       </c>
       <c r="C12" t="n">
-        <v>35.60716296089603</v>
+        <v>38.43477012120795</v>
       </c>
       <c r="D12" t="n">
-        <v>1.534159986253698</v>
+        <v>1.663091611145824</v>
       </c>
       <c r="E12" t="n">
-        <v>9.624683509164203</v>
+        <v>10.32228311238997</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539346061385988</v>
+        <v>0.7539215319292487</v>
       </c>
       <c r="G12" t="n">
-        <v>23.73619962901136</v>
+        <v>25.73924132546793</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68099188237553</v>
+        <v>34.68039046874544</v>
       </c>
       <c r="I12" t="n">
-        <v>2.740277774884352</v>
+        <v>2.754353011280976</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712091288366239</v>
+        <v>4.712009574557805</v>
       </c>
       <c r="K12" t="n">
-        <v>22.21766132380602</v>
+        <v>19.3747093644828</v>
       </c>
       <c r="L12" t="n">
-        <v>42.08394026386753</v>
+        <v>42.09881317867349</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90876454856958</v>
+        <v>99.90829266436424</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.27289297059539</v>
+        <v>78.37345232780208</v>
       </c>
       <c r="C13" t="n">
-        <v>33.52012616036988</v>
+        <v>36.60924830256242</v>
       </c>
       <c r="D13" t="n">
-        <v>1.425273538947357</v>
+        <v>1.565347330036017</v>
       </c>
       <c r="E13" t="n">
-        <v>9.322554492323956</v>
+        <v>10.09853815104136</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546977853915392</v>
+        <v>0.754658245116129</v>
       </c>
       <c r="G13" t="n">
-        <v>22.05153148923776</v>
+        <v>24.22647821439893</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71609812801079</v>
+        <v>34.71427927534194</v>
       </c>
       <c r="I13" t="n">
-        <v>2.285876377986877</v>
+        <v>2.297537079891903</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716861158697117</v>
+        <v>4.716614031975807</v>
       </c>
       <c r="K13" t="n">
-        <v>24.72710702940461</v>
+        <v>21.62654767219792</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67664798314539</v>
+        <v>41.68769421937073</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92388117291988</v>
+        <v>99.92349019413106</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.66612508913971</v>
+        <v>84.70263307439818</v>
       </c>
       <c r="C14" t="n">
-        <v>38.03948691720342</v>
+        <v>40.47478203371949</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4270609894178</v>
+        <v>1.567218414694868</v>
       </c>
       <c r="E14" t="n">
-        <v>11.83895455616532</v>
+        <v>12.28089405279087</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556442597872796</v>
+        <v>0.7555603001667995</v>
       </c>
       <c r="G14" t="n">
-        <v>24.06553283071963</v>
+        <v>25.91948941932783</v>
       </c>
       <c r="H14" t="n">
-        <v>36.74598223513578</v>
+        <v>36.41982671634681</v>
       </c>
       <c r="I14" t="n">
-        <v>3.110173594243403</v>
+        <v>3.037392295028512</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722776623670494</v>
+        <v>4.722251876042497</v>
       </c>
       <c r="K14" t="n">
-        <v>17.33387491086028</v>
+        <v>15.29736692560182</v>
       </c>
       <c r="L14" t="n">
-        <v>44.52309557265291</v>
+        <v>44.12672550780862</v>
       </c>
       <c r="M14" t="n">
-        <v>99.8964574007166</v>
+        <v>99.89887446712991</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.79915350899643</v>
+        <v>84.11033486694902</v>
       </c>
       <c r="C15" t="n">
-        <v>37.63539845246778</v>
+        <v>40.34403882581717</v>
       </c>
       <c r="D15" t="n">
-        <v>1.393465672511673</v>
+        <v>1.544398649299158</v>
       </c>
       <c r="E15" t="n">
-        <v>12.00948065504063</v>
+        <v>12.53305344177258</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7564431914587023</v>
+        <v>0.7563189721018634</v>
       </c>
       <c r="G15" t="n">
-        <v>23.51580029215611</v>
+        <v>25.55077795090719</v>
       </c>
       <c r="H15" t="n">
-        <v>36.80164213830314</v>
+        <v>36.46509044701484</v>
       </c>
       <c r="I15" t="n">
-        <v>2.594551612909272</v>
+        <v>2.53370183021675</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727769946616887</v>
+        <v>4.726993575636646</v>
       </c>
       <c r="K15" t="n">
-        <v>18.2008464910036</v>
+        <v>15.88966513305097</v>
       </c>
       <c r="L15" t="n">
-        <v>44.0773613455774</v>
+        <v>43.68192403293664</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91360628904877</v>
+        <v>99.91562799180478</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.19590220903034</v>
+        <v>81.83979786395221</v>
       </c>
       <c r="C16" t="n">
-        <v>35.4322929018829</v>
+        <v>38.46591504305853</v>
       </c>
       <c r="D16" t="n">
-        <v>1.296387993881898</v>
+        <v>1.457163996982815</v>
       </c>
       <c r="E16" t="n">
-        <v>11.53350649811175</v>
+        <v>12.17733556456312</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7571322066915556</v>
+        <v>0.7569699512780613</v>
       </c>
       <c r="G16" t="n">
-        <v>21.87754012650083</v>
+        <v>24.10755392842378</v>
       </c>
       <c r="H16" t="n">
-        <v>36.83516334956344</v>
+        <v>36.49647669463628</v>
       </c>
       <c r="I16" t="n">
-        <v>2.164095742458648</v>
+        <v>2.113235532580287</v>
       </c>
       <c r="J16" t="n">
-        <v>4.732076291822219</v>
+        <v>4.731062195487883</v>
       </c>
       <c r="K16" t="n">
-        <v>20.80409779096965</v>
+        <v>18.16020213604778</v>
       </c>
       <c r="L16" t="n">
-        <v>43.69153842901109</v>
+        <v>43.30350221449878</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92792912186364</v>
+        <v>99.92961939360508</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.11173376648279</v>
+        <v>83.48820134676784</v>
       </c>
       <c r="C17" t="n">
-        <v>36.79171461875883</v>
+        <v>39.67415935864996</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2975606760303</v>
+        <v>1.458389183396774</v>
       </c>
       <c r="E17" t="n">
-        <v>12.39154301347087</v>
+        <v>12.95112889801551</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7578170907131276</v>
+        <v>0.7576064131327339</v>
       </c>
       <c r="G17" t="n">
-        <v>22.37807475995553</v>
+        <v>24.54039297694066</v>
       </c>
       <c r="H17" t="n">
-        <v>37.34922829787681</v>
+        <v>36.93973237428609</v>
       </c>
       <c r="I17" t="n">
-        <v>2.201153111479111</v>
+        <v>2.105911418916473</v>
       </c>
       <c r="J17" t="n">
-        <v>4.736356816957045</v>
+        <v>4.735040082079586</v>
       </c>
       <c r="K17" t="n">
-        <v>18.88826623351721</v>
+        <v>16.51179865323217</v>
       </c>
       <c r="L17" t="n">
-        <v>44.24671368773967</v>
+        <v>43.74390391305496</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92669454001572</v>
+        <v>99.92986192493709</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.58338981635077</v>
+        <v>81.25070015401892</v>
       </c>
       <c r="C18" t="n">
-        <v>34.60236729996545</v>
+        <v>37.7625039758085</v>
       </c>
       <c r="D18" t="n">
-        <v>1.207539969792935</v>
+        <v>1.375601517805918</v>
       </c>
       <c r="E18" t="n">
-        <v>11.83781023174084</v>
+        <v>12.50863692649743</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7584071823105919</v>
+        <v>0.7581522550927451</v>
       </c>
       <c r="G18" t="n">
-        <v>20.82555384025041</v>
+        <v>23.14732048958772</v>
       </c>
       <c r="H18" t="n">
-        <v>37.3783111281012</v>
+        <v>36.96634679514097</v>
       </c>
       <c r="I18" t="n">
-        <v>1.835722574713619</v>
+        <v>1.756190575564465</v>
       </c>
       <c r="J18" t="n">
-        <v>4.740044889441196</v>
+        <v>4.738451594329656</v>
       </c>
       <c r="K18" t="n">
-        <v>21.41661018364923</v>
+        <v>18.74929984598108</v>
       </c>
       <c r="L18" t="n">
-        <v>43.91987937439977</v>
+        <v>43.42969863879608</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93885685801445</v>
+        <v>99.94150246058567</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.64971829718094</v>
+        <v>80.35488482632482</v>
       </c>
       <c r="C19" t="n">
-        <v>33.93734539796625</v>
+        <v>37.13781121900701</v>
       </c>
       <c r="D19" t="n">
-        <v>1.174482353519978</v>
+        <v>1.343140317093007</v>
       </c>
       <c r="E19" t="n">
-        <v>11.7710081806375</v>
+        <v>12.45752385771292</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7589097348385533</v>
+        <v>0.7586128053484898</v>
       </c>
       <c r="G19" t="n">
-        <v>20.25543344279405</v>
+        <v>22.6010941248647</v>
       </c>
       <c r="H19" t="n">
-        <v>37.40307957068256</v>
+        <v>36.98880252267603</v>
       </c>
       <c r="I19" t="n">
-        <v>1.543619171967329</v>
+        <v>1.464381165201618</v>
       </c>
       <c r="J19" t="n">
-        <v>4.743185842740955</v>
+        <v>4.741330033428061</v>
       </c>
       <c r="K19" t="n">
-        <v>22.35028170281908</v>
+        <v>19.64511517367516</v>
       </c>
       <c r="L19" t="n">
-        <v>43.6609529998059</v>
+        <v>43.16829053577435</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94858010059123</v>
+        <v>99.95121692845653</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.14250155764431</v>
+        <v>77.81509369796127</v>
       </c>
       <c r="C20" t="n">
-        <v>31.66700852391558</v>
+        <v>34.82396624960025</v>
       </c>
       <c r="D20" t="n">
-        <v>1.086409520615946</v>
+        <v>1.250081395233307</v>
       </c>
       <c r="E20" t="n">
-        <v>11.10283025971381</v>
+        <v>11.79790211210196</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7593430361750665</v>
+        <v>0.7590095718898376</v>
       </c>
       <c r="G20" t="n">
-        <v>18.73650606201276</v>
+        <v>21.03518665760797</v>
       </c>
       <c r="H20" t="n">
-        <v>37.42443494883058</v>
+        <v>37.00814825364979</v>
       </c>
       <c r="I20" t="n">
-        <v>1.287083754201972</v>
+        <v>1.220955883166943</v>
       </c>
       <c r="J20" t="n">
-        <v>4.745893976094163</v>
+        <v>4.743809824311485</v>
       </c>
       <c r="K20" t="n">
-        <v>24.85749844235571</v>
+        <v>22.1849063020387</v>
       </c>
       <c r="L20" t="n">
-        <v>43.4326147233963</v>
+        <v>42.95045019377211</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95712168966759</v>
+        <v>99.95932274541107</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.62035761709897</v>
+        <v>83.28551953322608</v>
       </c>
       <c r="C21" t="n">
-        <v>35.70042236447174</v>
+        <v>38.13211193920615</v>
       </c>
       <c r="D21" t="n">
-        <v>1.087223678508566</v>
+        <v>1.251007136196518</v>
       </c>
       <c r="E21" t="n">
-        <v>13.2732382684263</v>
+        <v>13.60701484984843</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7599120896621507</v>
+        <v>0.7595716522910398</v>
       </c>
       <c r="G21" t="n">
-        <v>20.60680230976309</v>
+        <v>22.54275682851364</v>
       </c>
       <c r="H21" t="n">
-        <v>39.30873597517609</v>
+        <v>38.52754711419891</v>
       </c>
       <c r="I21" t="n">
-        <v>1.834994735174328</v>
+        <v>1.850299125358551</v>
       </c>
       <c r="J21" t="n">
-        <v>4.749450560388439</v>
+        <v>4.747322826818998</v>
       </c>
       <c r="K21" t="n">
-        <v>18.37964238290103</v>
+        <v>16.71448046677392</v>
       </c>
       <c r="L21" t="n">
-        <v>45.85881456544389</v>
+        <v>45.09177659700686</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93887931281667</v>
+        <v>99.93836900298693</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_48_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_48_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.81165997138676</v>
+        <v>43.7465723589865</v>
       </c>
       <c r="M2" t="n">
-        <v>98.3682988271843</v>
+        <v>96.25274507537443</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.09942277745859</v>
+        <v>81.53963400708132</v>
       </c>
       <c r="C3" t="n">
-        <v>45.95376604546992</v>
+        <v>43.29518956263686</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228896457568935</v>
+        <v>2.183852664622686</v>
       </c>
       <c r="E3" t="n">
-        <v>5.724646717346261</v>
+        <v>4.152030290357296</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429654858563117</v>
+        <v>0.7376772230200596</v>
       </c>
       <c r="G3" t="n">
-        <v>33.98106898535329</v>
+        <v>32.84878383036624</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17641234939033</v>
+        <v>33.93315225892274</v>
       </c>
       <c r="I3" t="n">
-        <v>6.601898495341517</v>
+        <v>3.073655095916915</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643534286601948</v>
+        <v>4.610482643875372</v>
       </c>
       <c r="K3" t="n">
-        <v>11.9005772225414</v>
+        <v>18.4603659929187</v>
       </c>
       <c r="L3" t="n">
-        <v>48.90870006321484</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7630433312262</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.20381064139082</v>
+        <v>88.65943296022958</v>
       </c>
       <c r="C4" t="n">
-        <v>42.69889585663223</v>
+        <v>42.88307198239159</v>
       </c>
       <c r="D4" t="n">
-        <v>2.185889976398677</v>
+        <v>2.189614795165375</v>
       </c>
       <c r="E4" t="n">
-        <v>6.533052531514602</v>
+        <v>6.531894335185038</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445312047178082</v>
+        <v>0.7396235962925183</v>
       </c>
       <c r="G4" t="n">
-        <v>33.32540541762624</v>
+        <v>33.53508693408654</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24843541701917</v>
+        <v>34.02268542945584</v>
       </c>
       <c r="I4" t="n">
-        <v>5.513176064628031</v>
+        <v>7.017880393216029</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653320029486301</v>
+        <v>4.622647476828239</v>
       </c>
       <c r="K4" t="n">
-        <v>12.79618935860917</v>
+        <v>11.34056703977041</v>
       </c>
       <c r="L4" t="n">
-        <v>44.32152871544355</v>
+        <v>45.54304723348188</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81661393068495</v>
+        <v>99.76668625564389</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.18462051171036</v>
+        <v>87.6927705848847</v>
       </c>
       <c r="C5" t="n">
-        <v>42.53540789844186</v>
+        <v>43.00426289555349</v>
       </c>
       <c r="D5" t="n">
-        <v>2.136698934686172</v>
+        <v>2.144291905223311</v>
       </c>
       <c r="E5" t="n">
-        <v>7.15311534023625</v>
+        <v>7.373567704590929</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458565373406054</v>
+        <v>0.7412714434977468</v>
       </c>
       <c r="G5" t="n">
-        <v>32.57545394445768</v>
+        <v>32.84094335336766</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30940071766785</v>
+        <v>34.09848640089636</v>
       </c>
       <c r="I5" t="n">
-        <v>4.602491678943029</v>
+        <v>5.861263255447785</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661603358378784</v>
+        <v>4.632946521860917</v>
       </c>
       <c r="K5" t="n">
-        <v>13.81537948828964</v>
+        <v>12.30722941511528</v>
       </c>
       <c r="L5" t="n">
-        <v>43.4960688336955</v>
+        <v>44.49356656729744</v>
       </c>
       <c r="M5" t="n">
-        <v>99.846856220427</v>
+        <v>99.80505887796622</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.96957858720195</v>
+        <v>86.55271225479044</v>
       </c>
       <c r="C6" t="n">
-        <v>42.03531778762105</v>
+        <v>42.77408041761978</v>
       </c>
       <c r="D6" t="n">
-        <v>2.077812543394753</v>
+        <v>2.090512176830114</v>
       </c>
       <c r="E6" t="n">
-        <v>7.596177145068624</v>
+        <v>8.004234124934499</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469804596402064</v>
+        <v>0.7426684648010784</v>
       </c>
       <c r="G6" t="n">
-        <v>31.67769015737053</v>
+        <v>32.0172789029175</v>
       </c>
       <c r="H6" t="n">
-        <v>34.3611011434495</v>
+        <v>34.16274938084961</v>
       </c>
       <c r="I6" t="n">
-        <v>3.841189265527049</v>
+        <v>4.893591299450898</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668627872751291</v>
+        <v>4.641677905006739</v>
       </c>
       <c r="K6" t="n">
-        <v>15.03042141279805</v>
+        <v>13.44728774520957</v>
       </c>
       <c r="L6" t="n">
-        <v>42.80641380849916</v>
+        <v>43.61581896896376</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87215300891826</v>
+        <v>99.8371871317931</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.594437759543</v>
+        <v>85.15962076783485</v>
       </c>
       <c r="C7" t="n">
-        <v>41.25701798691614</v>
+        <v>42.14126764078469</v>
       </c>
       <c r="D7" t="n">
-        <v>2.011282549148271</v>
+        <v>2.024588437656298</v>
       </c>
       <c r="E7" t="n">
-        <v>7.887133603775275</v>
+        <v>8.432574840014199</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479351218955668</v>
+        <v>0.743855818857949</v>
       </c>
       <c r="G7" t="n">
-        <v>30.66339435354003</v>
+        <v>31.00762262497524</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40501560719608</v>
+        <v>34.21736766746566</v>
       </c>
       <c r="I7" t="n">
-        <v>3.205082012140493</v>
+        <v>4.084512511003346</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674594511847293</v>
+        <v>4.649098867862181</v>
       </c>
       <c r="K7" t="n">
-        <v>16.405562240457</v>
+        <v>14.84037923216514</v>
       </c>
       <c r="L7" t="n">
-        <v>42.23072007080665</v>
+        <v>42.88242003539877</v>
       </c>
       <c r="M7" t="n">
-        <v>99.8933002981798</v>
+        <v>99.86406690834859</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.58277230325776</v>
+        <v>83.65391024289303</v>
       </c>
       <c r="C8" t="n">
-        <v>43.64821738735294</v>
+        <v>41.27022460086786</v>
       </c>
       <c r="D8" t="n">
-        <v>2.015580009566738</v>
+        <v>1.953719373193159</v>
       </c>
       <c r="E8" t="n">
-        <v>9.781752634744407</v>
+        <v>8.705463307670508</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495332173910447</v>
+        <v>0.7448660707584417</v>
       </c>
       <c r="G8" t="n">
-        <v>31.1946136516699</v>
+        <v>29.92222612374761</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47852799998806</v>
+        <v>34.26383925488832</v>
       </c>
       <c r="I8" t="n">
-        <v>5.678182181203586</v>
+        <v>3.40838317039474</v>
       </c>
       <c r="J8" t="n">
-        <v>4.68458260869403</v>
+        <v>4.65541294224026</v>
       </c>
       <c r="K8" t="n">
-        <v>11.41722769674223</v>
+        <v>16.34608975710697</v>
       </c>
       <c r="L8" t="n">
-        <v>44.74568572890931</v>
+        <v>42.27022696116396</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81113081300448</v>
+        <v>99.88654131913879</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.83567460605349</v>
+        <v>82.03909493629754</v>
       </c>
       <c r="C9" t="n">
-        <v>42.78301823022389</v>
+        <v>40.18484612021794</v>
       </c>
       <c r="D9" t="n">
-        <v>1.937189980606987</v>
+        <v>1.878144452042803</v>
       </c>
       <c r="E9" t="n">
-        <v>10.19139175901993</v>
+        <v>8.842646954038489</v>
       </c>
       <c r="F9" t="n">
-        <v>0.750897137989152</v>
+        <v>0.7457266774739182</v>
       </c>
       <c r="G9" t="n">
-        <v>29.98139132562178</v>
+        <v>28.76475698515307</v>
       </c>
       <c r="H9" t="n">
-        <v>34.541268347501</v>
+        <v>34.30342716380024</v>
       </c>
       <c r="I9" t="n">
-        <v>4.740428942882449</v>
+        <v>2.843600969577035</v>
       </c>
       <c r="J9" t="n">
-        <v>4.693107112432201</v>
+        <v>4.660791734211988</v>
       </c>
       <c r="K9" t="n">
-        <v>13.16432539394648</v>
+        <v>17.96090506370247</v>
       </c>
       <c r="L9" t="n">
-        <v>43.89492909301841</v>
+        <v>41.75957150579087</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84227271718879</v>
+        <v>99.90532268971127</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.85047083206955</v>
+        <v>86.54218283523065</v>
       </c>
       <c r="C10" t="n">
-        <v>41.53405933798754</v>
+        <v>43.17742075644254</v>
       </c>
       <c r="D10" t="n">
-        <v>1.848733451496162</v>
+        <v>1.880376299802019</v>
       </c>
       <c r="E10" t="n">
-        <v>10.3854457313671</v>
+        <v>10.58507903577553</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520642588550392</v>
+        <v>0.7466128438240609</v>
       </c>
       <c r="G10" t="n">
-        <v>28.61237236458683</v>
+        <v>30.01666142586732</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59495590733181</v>
+        <v>35.56191334992486</v>
       </c>
       <c r="I10" t="n">
-        <v>3.956497500588612</v>
+        <v>3.085209606136467</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700401617843996</v>
+        <v>4.666330273900379</v>
       </c>
       <c r="K10" t="n">
-        <v>15.14952916793046</v>
+        <v>13.45781716476936</v>
       </c>
       <c r="L10" t="n">
-        <v>43.18473291233524</v>
+        <v>43.26204382135272</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86832141825325</v>
+        <v>99.89728174256463</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.78661179754089</v>
+        <v>86.44516652709697</v>
       </c>
       <c r="C11" t="n">
-        <v>40.0842703135249</v>
+        <v>43.49288037419433</v>
       </c>
       <c r="D11" t="n">
-        <v>1.757655617144975</v>
+        <v>1.870734506882406</v>
       </c>
       <c r="E11" t="n">
-        <v>10.42405086872862</v>
+        <v>11.00934837649263</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530639829588615</v>
+        <v>0.7473596718491968</v>
       </c>
       <c r="G11" t="n">
-        <v>27.20278413622035</v>
+        <v>29.90894323442875</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64094321610763</v>
+        <v>35.64368036164688</v>
       </c>
       <c r="I11" t="n">
-        <v>3.301464082887562</v>
+        <v>2.594102426739644</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706649893492885</v>
+        <v>4.670997949057479</v>
       </c>
       <c r="K11" t="n">
-        <v>17.21338820245911</v>
+        <v>13.55483347290303</v>
       </c>
       <c r="L11" t="n">
-        <v>42.59243877566631</v>
+        <v>42.86590248058027</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89009729165032</v>
+        <v>99.91361632767763</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.62529063551719</v>
+        <v>84.77849271950532</v>
       </c>
       <c r="C12" t="n">
-        <v>38.43477012120795</v>
+        <v>42.23000398577518</v>
       </c>
       <c r="D12" t="n">
-        <v>1.663091611145824</v>
+        <v>1.799397011850033</v>
       </c>
       <c r="E12" t="n">
-        <v>10.32228311238997</v>
+        <v>10.95012282590547</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539215319292487</v>
+        <v>0.7479954386969715</v>
       </c>
       <c r="G12" t="n">
-        <v>25.73924132546793</v>
+        <v>28.7684130942298</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68039046874544</v>
+        <v>35.67400186702132</v>
       </c>
       <c r="I12" t="n">
-        <v>2.754353011280976</v>
+        <v>2.163590989945657</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712009574557805</v>
+        <v>4.674971491856071</v>
       </c>
       <c r="K12" t="n">
-        <v>19.3747093644828</v>
+        <v>15.22150728049467</v>
       </c>
       <c r="L12" t="n">
-        <v>42.09881317867349</v>
+        <v>42.4764303329874</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90829266436424</v>
+        <v>99.92794159925725</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>78.37345232780208</v>
+        <v>85.99170707998242</v>
       </c>
       <c r="C13" t="n">
-        <v>36.60924830256242</v>
+        <v>43.22635819878824</v>
       </c>
       <c r="D13" t="n">
-        <v>1.565347330036017</v>
+        <v>1.800819701535416</v>
       </c>
       <c r="E13" t="n">
-        <v>10.09853815104136</v>
+        <v>11.60934804630537</v>
       </c>
       <c r="F13" t="n">
-        <v>0.754658245116129</v>
+        <v>0.7485868398098665</v>
       </c>
       <c r="G13" t="n">
-        <v>24.22647821439893</v>
+        <v>29.10178044567777</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71427927534194</v>
+        <v>36.01282910856239</v>
       </c>
       <c r="I13" t="n">
-        <v>2.297537079891903</v>
+        <v>2.039675189279942</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716614031975807</v>
+        <v>4.678667748811664</v>
       </c>
       <c r="K13" t="n">
-        <v>21.62654767219792</v>
+        <v>14.00829292001759</v>
       </c>
       <c r="L13" t="n">
-        <v>41.68769421937073</v>
+        <v>42.69741342125508</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92349019413106</v>
+        <v>99.93206454006091</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.70263307439818</v>
+        <v>84.30742071857657</v>
       </c>
       <c r="C14" t="n">
-        <v>40.47478203371949</v>
+        <v>41.85953689265592</v>
       </c>
       <c r="D14" t="n">
-        <v>1.567218414694868</v>
+        <v>1.730635843443286</v>
       </c>
       <c r="E14" t="n">
-        <v>12.28089405279087</v>
+        <v>11.44037235378022</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555603001667995</v>
+        <v>0.7490902556275409</v>
       </c>
       <c r="G14" t="n">
-        <v>25.91948941932783</v>
+        <v>27.96758848449126</v>
       </c>
       <c r="H14" t="n">
-        <v>36.41982671634681</v>
+        <v>36.03704731124554</v>
       </c>
       <c r="I14" t="n">
-        <v>3.037392295028512</v>
+        <v>1.700872372316591</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722251876042497</v>
+        <v>4.681814097672129</v>
       </c>
       <c r="K14" t="n">
-        <v>15.29736692560182</v>
+        <v>15.69257928142342</v>
       </c>
       <c r="L14" t="n">
-        <v>44.12672550780862</v>
+        <v>42.391226181774</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89887446712991</v>
+        <v>99.94334235585335</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>84.11033486694902</v>
+        <v>83.6057656343514</v>
       </c>
       <c r="C15" t="n">
-        <v>40.34403882581717</v>
+        <v>41.41413989208964</v>
       </c>
       <c r="D15" t="n">
-        <v>1.544398649299158</v>
+        <v>1.701688398042704</v>
       </c>
       <c r="E15" t="n">
-        <v>12.53305344177258</v>
+        <v>11.48669289068413</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563189721018634</v>
+        <v>0.749516164158649</v>
       </c>
       <c r="G15" t="n">
-        <v>25.55077795090719</v>
+        <v>27.49978918187773</v>
       </c>
       <c r="H15" t="n">
-        <v>36.46509044701484</v>
+        <v>36.0575368127048</v>
       </c>
       <c r="I15" t="n">
-        <v>2.53370183021675</v>
+        <v>1.426066160891823</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726993575636646</v>
+        <v>4.684476025991555</v>
       </c>
       <c r="K15" t="n">
-        <v>15.88966513305097</v>
+        <v>16.39423436564861</v>
       </c>
       <c r="L15" t="n">
-        <v>43.68192403293664</v>
+        <v>42.14411721537967</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91562799180478</v>
+        <v>99.95249147311792</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.83979786395221</v>
+        <v>81.48704609633931</v>
       </c>
       <c r="C16" t="n">
-        <v>38.46591504305853</v>
+        <v>39.51703184131944</v>
       </c>
       <c r="D16" t="n">
-        <v>1.457163996982815</v>
+        <v>1.613862405450451</v>
       </c>
       <c r="E16" t="n">
-        <v>12.17733556456312</v>
+        <v>11.09201322904442</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569699512780613</v>
+        <v>0.7498807004536975</v>
       </c>
       <c r="G16" t="n">
-        <v>24.10755392842378</v>
+        <v>26.08049509504368</v>
       </c>
       <c r="H16" t="n">
-        <v>36.49647669463628</v>
+        <v>36.0750738339284</v>
       </c>
       <c r="I16" t="n">
-        <v>2.113235532580287</v>
+        <v>1.18896645458305</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731062195487883</v>
+        <v>4.686754377835609</v>
       </c>
       <c r="K16" t="n">
-        <v>18.16020213604778</v>
+        <v>18.5129539036607</v>
       </c>
       <c r="L16" t="n">
-        <v>43.30350221449878</v>
+        <v>41.93040130610621</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92961939360508</v>
+        <v>99.96038705108634</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>83.48820134676784</v>
+        <v>85.68424333396639</v>
       </c>
       <c r="C17" t="n">
-        <v>39.67415935864996</v>
+        <v>42.19612793121114</v>
       </c>
       <c r="D17" t="n">
-        <v>1.458389183396774</v>
+        <v>1.614785748409252</v>
       </c>
       <c r="E17" t="n">
-        <v>12.95112889801551</v>
+        <v>12.55161530826351</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576064131327339</v>
+        <v>0.750309731492754</v>
       </c>
       <c r="G17" t="n">
-        <v>24.54039297694066</v>
+        <v>27.30355891466281</v>
       </c>
       <c r="H17" t="n">
-        <v>36.93973237428609</v>
+        <v>37.303855875791</v>
       </c>
       <c r="I17" t="n">
-        <v>2.105911418916473</v>
+        <v>1.470681933517343</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735040082079586</v>
+        <v>4.689435821829712</v>
       </c>
       <c r="K17" t="n">
-        <v>16.51179865323217</v>
+        <v>14.31575666603361</v>
       </c>
       <c r="L17" t="n">
-        <v>43.74390391305496</v>
+        <v>43.43912070309274</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92986192493709</v>
+        <v>99.95100530033748</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>81.25070015401892</v>
+        <v>87.20611917265869</v>
       </c>
       <c r="C18" t="n">
-        <v>37.7625039758085</v>
+        <v>42.95362921329485</v>
       </c>
       <c r="D18" t="n">
-        <v>1.375601517805918</v>
+        <v>1.616136338897633</v>
       </c>
       <c r="E18" t="n">
-        <v>12.50863692649743</v>
+        <v>13.17299247110813</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581522550927451</v>
+        <v>0.7509372829729994</v>
       </c>
       <c r="G18" t="n">
-        <v>23.14732048958772</v>
+        <v>27.4494891018985</v>
       </c>
       <c r="H18" t="n">
-        <v>36.96634679514097</v>
+        <v>37.33505644402452</v>
       </c>
       <c r="I18" t="n">
-        <v>1.756190575564465</v>
+        <v>2.188149515175651</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738451594329656</v>
+        <v>4.693358018581246</v>
       </c>
       <c r="K18" t="n">
-        <v>18.74929984598108</v>
+        <v>12.79388082734133</v>
       </c>
       <c r="L18" t="n">
-        <v>43.42969863879608</v>
+        <v>44.17961259608178</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94150246058567</v>
+        <v>99.92712263671795</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>80.35488482632482</v>
+        <v>84.78166376459004</v>
       </c>
       <c r="C19" t="n">
-        <v>37.13781121900701</v>
+        <v>40.86900944169415</v>
       </c>
       <c r="D19" t="n">
-        <v>1.343140317093007</v>
+        <v>1.52446461559809</v>
       </c>
       <c r="E19" t="n">
-        <v>12.45752385771292</v>
+        <v>12.72991159331246</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586128053484898</v>
+        <v>0.7514760334807128</v>
       </c>
       <c r="G19" t="n">
-        <v>22.6010941248647</v>
+        <v>25.89247815604015</v>
       </c>
       <c r="H19" t="n">
-        <v>36.98880252267603</v>
+        <v>37.36184201063681</v>
       </c>
       <c r="I19" t="n">
-        <v>1.464381165201618</v>
+        <v>1.824766146267356</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741330033428061</v>
+        <v>4.696725209254454</v>
       </c>
       <c r="K19" t="n">
-        <v>19.64511517367516</v>
+        <v>15.21833623540996</v>
       </c>
       <c r="L19" t="n">
-        <v>43.16829053577435</v>
+        <v>43.85187239191881</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95121692845653</v>
+        <v>99.93921806902291</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.81509369796127</v>
+        <v>82.23071016482922</v>
       </c>
       <c r="C20" t="n">
-        <v>34.82396624960025</v>
+        <v>38.60081654120772</v>
       </c>
       <c r="D20" t="n">
-        <v>1.250081395233307</v>
+        <v>1.428479811821778</v>
       </c>
       <c r="E20" t="n">
-        <v>11.79790211210196</v>
+        <v>12.18199474789343</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590095718898376</v>
+        <v>0.7519395375959754</v>
       </c>
       <c r="G20" t="n">
-        <v>21.03518665760797</v>
+        <v>24.26221110381677</v>
       </c>
       <c r="H20" t="n">
-        <v>37.00814825364979</v>
+        <v>37.38488648145714</v>
       </c>
       <c r="I20" t="n">
-        <v>1.220955883166943</v>
+        <v>1.521576372269276</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743809824311485</v>
+        <v>4.699622109974846</v>
       </c>
       <c r="K20" t="n">
-        <v>22.1849063020387</v>
+        <v>17.76928983517078</v>
       </c>
       <c r="L20" t="n">
-        <v>42.95045019377211</v>
+        <v>43.57920567511406</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95932274541107</v>
+        <v>99.94931205149257</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>83.28551953322608</v>
+        <v>79.74231352878301</v>
       </c>
       <c r="C21" t="n">
-        <v>38.13211193920615</v>
+        <v>36.3475586167858</v>
       </c>
       <c r="D21" t="n">
-        <v>1.251007136196518</v>
+        <v>1.335330376880193</v>
       </c>
       <c r="E21" t="n">
-        <v>13.60701484984843</v>
+        <v>11.59906377719879</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595716522910398</v>
+        <v>0.7523383012763152</v>
       </c>
       <c r="G21" t="n">
-        <v>22.54275682851364</v>
+        <v>22.68010176208815</v>
       </c>
       <c r="H21" t="n">
-        <v>38.52754711419891</v>
+        <v>37.40471219107481</v>
       </c>
       <c r="I21" t="n">
-        <v>1.850299125358551</v>
+        <v>1.268652737287774</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747322826818998</v>
+        <v>4.702114382976969</v>
       </c>
       <c r="K21" t="n">
-        <v>16.71448046677392</v>
+        <v>20.257686471217</v>
       </c>
       <c r="L21" t="n">
-        <v>45.09177659700686</v>
+        <v>43.35248890165638</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93836900298693</v>
+        <v>99.95773398965918</v>
       </c>
     </row>
   </sheetData>
